--- a/sports_forms/013_cutting_phase_weight_training_plan_form--sports_forms.xlsx
+++ b/sports_forms/013_cutting_phase_weight_training_plan_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,8 +761,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,12 +790,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'chest'}</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Chest'}</t>
+          <t>Chest</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'back'}</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Back'}</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'shoulders'}</t>
+          <t>shoulders</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Shoulders'}</t>
+          <t>Shoulders</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'legs'}</t>
+          <t>legs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Legs'}</t>
+          <t>Legs</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'core'}</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Core'}</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'cardio'}</t>
+          <t>cardio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Cardio'}</t>
+          <t>Cardio</t>
         </is>
       </c>
     </row>
